--- a/jogos_2025-11-01.xlsx
+++ b/jogos_2025-11-01.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK264"/>
+  <dimension ref="A1:AK267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -843,10 +843,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45962.33333333334</v>
+        <v>45962.3125</v>
       </c>
     </row>
     <row r="19">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Costa Adeje Tenerife W</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Costa Adeje Tenerife W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45962.35416666666</v>
+        <v>45962.33333333334</v>
       </c>
     </row>
     <row r="27">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4111,27 +4111,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45962.35763888889</v>
+        <v>45962.35416666666</v>
       </c>
     </row>
     <row r="30">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45962.375</v>
+        <v>45962.35763888889</v>
       </c>
     </row>
     <row r="31">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Tusker</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tusker</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6046,27 +6046,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45962.38541666666</v>
+        <v>45962.375</v>
       </c>
     </row>
     <row r="45">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45962.39583333334</v>
+        <v>45962.38541666666</v>
       </c>
     </row>
     <row r="48">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,22 +6825,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7198,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="AK52" s="3" t="n">
-        <v>45962.40625</v>
+        <v>45962.39583333334</v>
       </c>
     </row>
     <row r="53">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45962.41666666666</v>
+        <v>45962.40625</v>
       </c>
     </row>
     <row r="54">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,22 +8244,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,22 +8373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9405,22 +9405,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9534,22 +9534,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9658,12 +9658,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9778,7 +9778,7 @@
         <v>0</v>
       </c>
       <c r="AK72" s="3" t="n">
-        <v>45962.4375</v>
+        <v>45962.41666666666</v>
       </c>
     </row>
     <row r="73">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10948,27 +10948,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11068,7 +11068,7 @@
         <v>0</v>
       </c>
       <c r="AK82" s="3" t="n">
-        <v>45962.45833333334</v>
+        <v>45962.4375</v>
       </c>
     </row>
     <row r="83">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11197,7 +11197,7 @@
         <v>0</v>
       </c>
       <c r="AK83" s="3" t="n">
-        <v>45962.45833333334</v>
+        <v>45962.4375</v>
       </c>
     </row>
     <row r="84">
@@ -11206,7 +11206,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11326,7 +11326,7 @@
         <v>0</v>
       </c>
       <c r="AK84" s="3" t="n">
-        <v>45962.45833333334</v>
+        <v>45962.4375</v>
       </c>
     </row>
     <row r="85">
@@ -11335,7 +11335,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11455,7 +11455,7 @@
         <v>0</v>
       </c>
       <c r="AK85" s="3" t="n">
-        <v>45962.45833333334</v>
+        <v>45962.4375</v>
       </c>
     </row>
     <row r="86">
@@ -11464,12 +11464,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11584,7 +11584,7 @@
         <v>0</v>
       </c>
       <c r="AK86" s="3" t="n">
-        <v>45962.45833333334</v>
+        <v>45962.4375</v>
       </c>
     </row>
     <row r="87">
@@ -11598,22 +11598,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,22 +11727,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,22 +11985,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,22 +12243,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,22 +12372,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12453,10 +12453,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -12501,22 +12501,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,22 +12888,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13017,22 +13017,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,22 +13146,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,22 +13404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,22 +13662,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14388,10 +14388,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15076,27 +15076,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15196,7 +15196,7 @@
         <v>0</v>
       </c>
       <c r="AK114" s="3" t="n">
-        <v>45962.47916666666</v>
+        <v>45962.45833333334</v>
       </c>
     </row>
     <row r="115">
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,16 +15285,16 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z115" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.95</v>
+        <v>3.5</v>
       </c>
       <c r="M116" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="N116" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15420,10 +15420,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,16 +15543,16 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z117" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="M118" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="N118" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,16 +15672,16 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z118" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="M120" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="N120" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,16 +15930,16 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z120" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA120" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -15979,12 +15979,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16099,7 +16099,7 @@
         <v>0</v>
       </c>
       <c r="AK121" s="3" t="n">
-        <v>45962.48263888889</v>
+        <v>45962.47916666666</v>
       </c>
     </row>
     <row r="122">
@@ -16108,12 +16108,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16228,7 +16228,7 @@
         <v>0</v>
       </c>
       <c r="AK122" s="3" t="n">
-        <v>45962.5</v>
+        <v>45962.48263888889</v>
       </c>
     </row>
     <row r="123">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z127" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18048,7 +18048,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18058,12 +18058,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18177,7 +18177,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18187,12 +18187,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18316,12 +18316,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18435,7 +18435,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18445,12 +18445,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18574,12 +18574,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18693,22 +18693,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -18822,22 +18822,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19080,7 +19080,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19090,12 +19090,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19219,12 +19219,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19245,13 +19245,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -19284,10 +19284,10 @@
         <v>0</v>
       </c>
       <c r="Y146" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z146" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA146" t="n">
         <v>0</v>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19374,13 +19374,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N147" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -19413,10 +19413,10 @@
         <v>0</v>
       </c>
       <c r="Y147" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z147" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA147" t="n">
         <v>0</v>
@@ -19467,7 +19467,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19477,12 +19477,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19503,13 +19503,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M148" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N148" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -19542,10 +19542,10 @@
         <v>0</v>
       </c>
       <c r="Y148" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z148" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA148" t="n">
         <v>0</v>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -19606,12 +19606,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -19735,12 +19735,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -19854,7 +19854,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -19864,12 +19864,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -19890,13 +19890,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M151" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N151" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -19929,10 +19929,10 @@
         <v>0</v>
       </c>
       <c r="Y151" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z151" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA151" t="n">
         <v>0</v>
@@ -19983,7 +19983,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -19993,12 +19993,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20112,7 +20112,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20122,12 +20122,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20148,13 +20148,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -20187,10 +20187,10 @@
         <v>0</v>
       </c>
       <c r="Y153" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z153" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA153" t="n">
         <v>0</v>
@@ -20251,12 +20251,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20370,7 +20370,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20380,12 +20380,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20499,7 +20499,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -20509,12 +20509,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -20535,13 +20535,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M156" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -20574,10 +20574,10 @@
         <v>0</v>
       </c>
       <c r="Y156" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z156" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA156" t="n">
         <v>0</v>
@@ -20628,7 +20628,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -20638,12 +20638,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -20664,13 +20664,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M157" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -20703,10 +20703,10 @@
         <v>0</v>
       </c>
       <c r="Y157" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA157" t="n">
         <v>0</v>
@@ -20757,7 +20757,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -20767,12 +20767,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -20793,13 +20793,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -20832,10 +20832,10 @@
         <v>0</v>
       </c>
       <c r="Y158" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z158" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA158" t="n">
         <v>0</v>
@@ -20886,7 +20886,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -20896,12 +20896,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21025,12 +21025,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21051,13 +21051,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M160" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -21090,10 +21090,10 @@
         <v>0</v>
       </c>
       <c r="Y160" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z160" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA160" t="n">
         <v>0</v>
@@ -21139,12 +21139,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21154,12 +21154,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21180,13 +21180,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M161" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N161" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -21219,10 +21219,10 @@
         <v>0</v>
       </c>
       <c r="Y161" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z161" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA161" t="n">
         <v>0</v>
@@ -21259,7 +21259,7 @@
         <v>0</v>
       </c>
       <c r="AK161" s="3" t="n">
-        <v>45962.51041666666</v>
+        <v>45962.5</v>
       </c>
     </row>
     <row r="162">
@@ -21268,12 +21268,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21283,12 +21283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21309,13 +21309,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -21348,10 +21348,10 @@
         <v>0</v>
       </c>
       <c r="Y162" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z162" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA162" t="n">
         <v>0</v>
@@ -21388,7 +21388,7 @@
         <v>0</v>
       </c>
       <c r="AK162" s="3" t="n">
-        <v>45962.52083333334</v>
+        <v>45962.51041666666</v>
       </c>
     </row>
     <row r="163">
@@ -21402,7 +21402,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21412,12 +21412,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21531,7 +21531,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -21541,12 +21541,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -21567,13 +21567,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M164" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N164" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -21612,10 +21612,10 @@
         <v>0</v>
       </c>
       <c r="AA164" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB164" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC164" t="n">
         <v>0</v>
@@ -21660,7 +21660,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -21670,12 +21670,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -21799,12 +21799,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -21864,10 +21864,10 @@
         <v>0</v>
       </c>
       <c r="Y166" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z166" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA166" t="n">
         <v>0</v>
@@ -21918,7 +21918,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -21928,12 +21928,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -22047,7 +22047,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -22057,12 +22057,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22083,13 +22083,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M168" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="Y168" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z168" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA168" t="n">
         <v>0</v>
@@ -22176,7 +22176,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22186,12 +22186,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22212,13 +22212,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -22251,10 +22251,10 @@
         <v>0</v>
       </c>
       <c r="Y169" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z169" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA169" t="n">
         <v>0</v>
@@ -22305,7 +22305,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -22315,12 +22315,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22341,13 +22341,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M170" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N170" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -22386,10 +22386,10 @@
         <v>0</v>
       </c>
       <c r="AA170" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB170" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC170" t="n">
         <v>0</v>
@@ -22429,12 +22429,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22444,12 +22444,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -22549,7 +22549,7 @@
         <v>0</v>
       </c>
       <c r="AK171" s="3" t="n">
-        <v>45962.53125</v>
+        <v>45962.52083333334</v>
       </c>
     </row>
     <row r="172">
@@ -22558,12 +22558,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -22573,12 +22573,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -22678,7 +22678,7 @@
         <v>0</v>
       </c>
       <c r="AK172" s="3" t="n">
-        <v>45962.54166666666</v>
+        <v>45962.53125</v>
       </c>
     </row>
     <row r="173">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -22728,13 +22728,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M173" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N173" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -22767,10 +22767,10 @@
         <v>0</v>
       </c>
       <c r="Y173" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z173" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA173" t="n">
         <v>0</v>
@@ -22821,7 +22821,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -22831,12 +22831,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -22960,12 +22960,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23089,12 +23089,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23208,7 +23208,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23218,12 +23218,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23337,7 +23337,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -23347,12 +23347,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23373,13 +23373,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M178" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N178" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -23412,10 +23412,10 @@
         <v>0</v>
       </c>
       <c r="Y178" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z178" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA178" t="n">
         <v>0</v>
@@ -23466,7 +23466,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -23476,12 +23476,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -23502,13 +23502,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M179" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N179" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -23541,10 +23541,10 @@
         <v>0</v>
       </c>
       <c r="Y179" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z179" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA179" t="n">
         <v>0</v>
@@ -23595,7 +23595,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -23605,12 +23605,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -23631,13 +23631,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M180" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N180" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -23670,10 +23670,10 @@
         <v>0</v>
       </c>
       <c r="Y180" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z180" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA180" t="n">
         <v>0</v>
@@ -23734,12 +23734,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -23863,12 +23863,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -24111,7 +24111,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -24121,12 +24121,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24147,13 +24147,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M184" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N184" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -24186,10 +24186,10 @@
         <v>0</v>
       </c>
       <c r="Y184" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z184" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA184" t="n">
         <v>0</v>
@@ -24240,7 +24240,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -24250,12 +24250,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24276,13 +24276,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N185" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -24315,10 +24315,10 @@
         <v>0</v>
       </c>
       <c r="Y185" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z185" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA185" t="n">
         <v>0</v>
@@ -24379,12 +24379,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24498,7 +24498,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -24508,12 +24508,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -24534,13 +24534,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M187" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N187" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -24573,10 +24573,10 @@
         <v>0</v>
       </c>
       <c r="Y187" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z187" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA187" t="n">
         <v>0</v>
@@ -24627,7 +24627,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -24637,12 +24637,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -24663,13 +24663,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N188" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -24702,10 +24702,10 @@
         <v>0</v>
       </c>
       <c r="Y188" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z188" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA188" t="n">
         <v>0</v>
@@ -24751,12 +24751,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -24766,12 +24766,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -24871,7 +24871,7 @@
         <v>0</v>
       </c>
       <c r="AK189" s="3" t="n">
-        <v>45962.55208333334</v>
+        <v>45962.54166666666</v>
       </c>
     </row>
     <row r="190">
@@ -24880,27 +24880,27 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25000,7 +25000,7 @@
         <v>0</v>
       </c>
       <c r="AK190" s="3" t="n">
-        <v>45962.5625</v>
+        <v>45962.55208333334</v>
       </c>
     </row>
     <row r="191">
@@ -25024,12 +25024,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25143,22 +25143,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25282,12 +25282,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25401,22 +25401,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -25530,7 +25530,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -25540,12 +25540,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -25566,13 +25566,13 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M195" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N195" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -25605,16 +25605,16 @@
         <v>0</v>
       </c>
       <c r="Y195" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z195" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA195" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB195" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC195" t="n">
         <v>0</v>
@@ -25659,7 +25659,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -25669,12 +25669,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -25788,22 +25788,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -25824,13 +25824,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M197" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N197" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -25863,16 +25863,16 @@
         <v>0</v>
       </c>
       <c r="Y197" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z197" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AA197" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB197" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC197" t="n">
         <v>0</v>
@@ -25917,22 +25917,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26046,22 +26046,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26170,12 +26170,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26185,12 +26185,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26290,7 +26290,7 @@
         <v>0</v>
       </c>
       <c r="AK200" s="3" t="n">
-        <v>45962.58333333334</v>
+        <v>45962.5625</v>
       </c>
     </row>
     <row r="201">
@@ -26304,7 +26304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26314,12 +26314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26433,7 +26433,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -26443,12 +26443,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -26691,7 +26691,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -26701,12 +26701,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -26820,7 +26820,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -26830,12 +26830,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -26949,7 +26949,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -26959,12 +26959,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27078,22 +27078,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27207,22 +27207,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27336,7 +27336,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -27346,12 +27346,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27465,7 +27465,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -27475,12 +27475,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -27604,12 +27604,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27723,7 +27723,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -27733,12 +27733,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -27847,12 +27847,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -27862,12 +27862,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -27888,13 +27888,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M213" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="N213" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -27933,10 +27933,10 @@
         <v>0</v>
       </c>
       <c r="AA213" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB213" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC213" t="n">
         <v>0</v>
@@ -27967,7 +27967,7 @@
         <v>0</v>
       </c>
       <c r="AK213" s="3" t="n">
-        <v>45962.59375</v>
+        <v>45962.58333333334</v>
       </c>
     </row>
     <row r="214">
@@ -27976,7 +27976,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -27991,12 +27991,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28096,7 +28096,7 @@
         <v>0</v>
       </c>
       <c r="AK214" s="3" t="n">
-        <v>45962.60416666666</v>
+        <v>45962.58333333334</v>
       </c>
     </row>
     <row r="215">
@@ -28105,12 +28105,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -28120,12 +28120,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28146,13 +28146,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M215" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="N215" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -28185,16 +28185,16 @@
         <v>0</v>
       </c>
       <c r="Y215" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z215" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA215" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB215" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC215" t="n">
         <v>0</v>
@@ -28225,7 +28225,7 @@
         <v>0</v>
       </c>
       <c r="AK215" s="3" t="n">
-        <v>45962.60416666666</v>
+        <v>45962.58333333334</v>
       </c>
     </row>
     <row r="216">
@@ -28234,12 +28234,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28249,12 +28249,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28275,13 +28275,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>2.7</v>
+        <v>1.19</v>
       </c>
       <c r="M216" t="n">
-        <v>3.7</v>
+        <v>6.9</v>
       </c>
       <c r="N216" t="n">
-        <v>2.4</v>
+        <v>15</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -28314,16 +28314,16 @@
         <v>0</v>
       </c>
       <c r="Y216" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z216" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA216" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB216" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC216" t="n">
         <v>0</v>
@@ -28354,7 +28354,7 @@
         <v>0</v>
       </c>
       <c r="AK216" s="3" t="n">
-        <v>45962.60416666666</v>
+        <v>45962.59375</v>
       </c>
     </row>
     <row r="217">
@@ -28368,7 +28368,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -28378,12 +28378,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -28404,13 +28404,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M217" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N217" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -28443,10 +28443,10 @@
         <v>0</v>
       </c>
       <c r="Y217" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z217" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA217" t="n">
         <v>0</v>
@@ -28497,7 +28497,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -28507,12 +28507,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -28533,13 +28533,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M218" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="N218" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -28572,16 +28572,16 @@
         <v>0</v>
       </c>
       <c r="Y218" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z218" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA218" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB218" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC218" t="n">
         <v>0</v>
@@ -28626,7 +28626,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -28636,12 +28636,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -28662,13 +28662,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N219" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -28701,10 +28701,10 @@
         <v>0</v>
       </c>
       <c r="Y219" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Z219" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA219" t="n">
         <v>0</v>
@@ -29008,12 +29008,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29023,12 +29023,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29049,13 +29049,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N222" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -29094,10 +29094,10 @@
         <v>0</v>
       </c>
       <c r="AA222" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB222" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC222" t="n">
         <v>0</v>
@@ -29128,7 +29128,7 @@
         <v>0</v>
       </c>
       <c r="AK222" s="3" t="n">
-        <v>45962.61458333334</v>
+        <v>45962.60416666666</v>
       </c>
     </row>
     <row r="223">
@@ -29137,12 +29137,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29178,13 +29178,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M223" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N223" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -29217,10 +29217,10 @@
         <v>0</v>
       </c>
       <c r="Y223" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Z223" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA223" t="n">
         <v>0</v>
@@ -29257,7 +29257,7 @@
         <v>0</v>
       </c>
       <c r="AK223" s="3" t="n">
-        <v>45962.61458333334</v>
+        <v>45962.60416666666</v>
       </c>
     </row>
     <row r="224">
@@ -29266,12 +29266,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29281,12 +29281,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29307,13 +29307,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M224" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N224" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -29346,10 +29346,10 @@
         <v>0</v>
       </c>
       <c r="Y224" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z224" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA224" t="n">
         <v>0</v>
@@ -29386,7 +29386,7 @@
         <v>0</v>
       </c>
       <c r="AK224" s="3" t="n">
-        <v>45962.61458333334</v>
+        <v>45962.60416666666</v>
       </c>
     </row>
     <row r="225">
@@ -29395,12 +29395,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -29410,12 +29410,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -29515,7 +29515,7 @@
         <v>0</v>
       </c>
       <c r="AK225" s="3" t="n">
-        <v>45962.625</v>
+        <v>45962.61458333334</v>
       </c>
     </row>
     <row r="226">
@@ -29524,12 +29524,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -29539,12 +29539,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -29565,13 +29565,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M226" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N226" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -29604,10 +29604,10 @@
         <v>0</v>
       </c>
       <c r="Y226" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z226" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA226" t="n">
         <v>0</v>
@@ -29644,7 +29644,7 @@
         <v>0</v>
       </c>
       <c r="AK226" s="3" t="n">
-        <v>45962.625</v>
+        <v>45962.61458333334</v>
       </c>
     </row>
     <row r="227">
@@ -29653,12 +29653,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -29668,12 +29668,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -29694,13 +29694,13 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M227" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N227" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -29739,10 +29739,10 @@
         <v>0</v>
       </c>
       <c r="AA227" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB227" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC227" t="n">
         <v>0</v>
@@ -29773,7 +29773,7 @@
         <v>0</v>
       </c>
       <c r="AK227" s="3" t="n">
-        <v>45962.625</v>
+        <v>45962.61458333334</v>
       </c>
     </row>
     <row r="228">
@@ -29787,7 +29787,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -29797,12 +29797,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -29823,13 +29823,13 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M228" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N228" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="O228" t="n">
         <v>0</v>
@@ -29862,10 +29862,10 @@
         <v>0</v>
       </c>
       <c r="Y228" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z228" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA228" t="n">
         <v>0</v>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -29926,12 +29926,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -29952,13 +29952,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M229" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N229" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -29991,10 +29991,10 @@
         <v>0</v>
       </c>
       <c r="Y229" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z229" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA229" t="n">
         <v>0</v>
@@ -30045,7 +30045,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -30055,12 +30055,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30174,7 +30174,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -30184,12 +30184,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30298,12 +30298,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -30339,13 +30339,13 @@
         </is>
       </c>
       <c r="L232" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="M232" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N232" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O232" t="n">
         <v>0</v>
@@ -30378,10 +30378,10 @@
         <v>0</v>
       </c>
       <c r="Y232" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z232" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA232" t="n">
         <v>0</v>
@@ -30418,7 +30418,7 @@
         <v>0</v>
       </c>
       <c r="AK232" s="3" t="n">
-        <v>45962.64583333334</v>
+        <v>45962.625</v>
       </c>
     </row>
     <row r="233">
@@ -30427,12 +30427,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -30442,12 +30442,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -30547,7 +30547,7 @@
         <v>0</v>
       </c>
       <c r="AK233" s="3" t="n">
-        <v>45962.64583333334</v>
+        <v>45962.625</v>
       </c>
     </row>
     <row r="234">
@@ -30556,12 +30556,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -30571,12 +30571,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -30676,7 +30676,7 @@
         <v>0</v>
       </c>
       <c r="AK234" s="3" t="n">
-        <v>45962.66666666666</v>
+        <v>45962.625</v>
       </c>
     </row>
     <row r="235">
@@ -30685,12 +30685,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -30700,12 +30700,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -30726,13 +30726,13 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M235" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N235" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O235" t="n">
         <v>0</v>
@@ -30765,10 +30765,10 @@
         <v>0</v>
       </c>
       <c r="Y235" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z235" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA235" t="n">
         <v>0</v>
@@ -30805,7 +30805,7 @@
         <v>0</v>
       </c>
       <c r="AK235" s="3" t="n">
-        <v>45962.66666666666</v>
+        <v>45962.64583333334</v>
       </c>
     </row>
     <row r="236">
@@ -30814,12 +30814,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -30829,12 +30829,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -30934,7 +30934,7 @@
         <v>0</v>
       </c>
       <c r="AK236" s="3" t="n">
-        <v>45962.66666666666</v>
+        <v>45962.64583333334</v>
       </c>
     </row>
     <row r="237">
@@ -30948,7 +30948,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -30958,12 +30958,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31077,22 +31077,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31206,22 +31206,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M239" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N239" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -31281,10 +31281,10 @@
         <v>0</v>
       </c>
       <c r="Y239" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z239" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA239" t="n">
         <v>0</v>
@@ -31335,22 +31335,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -31371,13 +31371,13 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M240" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N240" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -31410,10 +31410,10 @@
         <v>0</v>
       </c>
       <c r="Y240" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z240" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA240" t="n">
         <v>0</v>
@@ -31464,7 +31464,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -31474,12 +31474,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -31593,7 +31593,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -31603,12 +31603,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -31722,22 +31722,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -31846,27 +31846,27 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -31966,7 +31966,7 @@
         <v>0</v>
       </c>
       <c r="AK244" s="3" t="n">
-        <v>45962.6875</v>
+        <v>45962.66666666666</v>
       </c>
     </row>
     <row r="245">
@@ -31975,27 +31975,27 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32095,7 +32095,7 @@
         <v>0</v>
       </c>
       <c r="AK245" s="3" t="n">
-        <v>45962.6875</v>
+        <v>45962.66666666666</v>
       </c>
     </row>
     <row r="246">
@@ -32104,27 +32104,27 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -32224,7 +32224,7 @@
         <v>0</v>
       </c>
       <c r="AK246" s="3" t="n">
-        <v>45962.6875</v>
+        <v>45962.66666666666</v>
       </c>
     </row>
     <row r="247">
@@ -32233,12 +32233,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -32248,12 +32248,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -32353,7 +32353,7 @@
         <v>0</v>
       </c>
       <c r="AK247" s="3" t="n">
-        <v>45962.69791666666</v>
+        <v>45962.6875</v>
       </c>
     </row>
     <row r="248">
@@ -32362,12 +32362,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -32377,12 +32377,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -32482,7 +32482,7 @@
         <v>0</v>
       </c>
       <c r="AK248" s="3" t="n">
-        <v>45962.69791666666</v>
+        <v>45962.6875</v>
       </c>
     </row>
     <row r="249">
@@ -32491,27 +32491,27 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -32532,13 +32532,13 @@
         </is>
       </c>
       <c r="L249" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M249" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N249" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O249" t="n">
         <v>0</v>
@@ -32571,16 +32571,16 @@
         <v>0</v>
       </c>
       <c r="Y249" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z249" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA249" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB249" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC249" t="n">
         <v>0</v>
@@ -32611,7 +32611,7 @@
         <v>0</v>
       </c>
       <c r="AK249" s="3" t="n">
-        <v>45962.70833333334</v>
+        <v>45962.6875</v>
       </c>
     </row>
     <row r="250">
@@ -32620,12 +32620,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -32635,12 +32635,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -32661,13 +32661,13 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M250" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N250" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O250" t="n">
         <v>0</v>
@@ -32706,10 +32706,10 @@
         <v>0</v>
       </c>
       <c r="AA250" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB250" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC250" t="n">
         <v>0</v>
@@ -32740,7 +32740,7 @@
         <v>0</v>
       </c>
       <c r="AK250" s="3" t="n">
-        <v>45962.70833333334</v>
+        <v>45962.69791666666</v>
       </c>
     </row>
     <row r="251">
@@ -32749,12 +32749,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -32764,12 +32764,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>CE Europa</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -32869,7 +32869,7 @@
         <v>0</v>
       </c>
       <c r="AK251" s="3" t="n">
-        <v>45962.70833333334</v>
+        <v>45962.69791666666</v>
       </c>
     </row>
     <row r="252">
@@ -32878,12 +32878,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -32893,12 +32893,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -32919,13 +32919,13 @@
         </is>
       </c>
       <c r="L252" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M252" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N252" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O252" t="n">
         <v>0</v>
@@ -32964,10 +32964,10 @@
         <v>0</v>
       </c>
       <c r="AA252" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB252" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC252" t="n">
         <v>0</v>
@@ -32998,7 +32998,7 @@
         <v>0</v>
       </c>
       <c r="AK252" s="3" t="n">
-        <v>45962.71180555555</v>
+        <v>45962.70833333334</v>
       </c>
     </row>
     <row r="253">
@@ -33007,12 +33007,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -33022,12 +33022,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -33048,13 +33048,13 @@
         </is>
       </c>
       <c r="L253" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M253" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N253" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O253" t="n">
         <v>0</v>
@@ -33087,16 +33087,16 @@
         <v>0</v>
       </c>
       <c r="Y253" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z253" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA253" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB253" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC253" t="n">
         <v>0</v>
@@ -33127,7 +33127,7 @@
         <v>0</v>
       </c>
       <c r="AK253" s="3" t="n">
-        <v>45962.72916666666</v>
+        <v>45962.70833333334</v>
       </c>
     </row>
     <row r="254">
@@ -33136,27 +33136,27 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>CE Europa</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -33256,7 +33256,7 @@
         <v>0</v>
       </c>
       <c r="AK254" s="3" t="n">
-        <v>45962.75</v>
+        <v>45962.70833333334</v>
       </c>
     </row>
     <row r="255">
@@ -33265,27 +33265,27 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="L255" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M255" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N255" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O255" t="n">
         <v>0</v>
@@ -33345,10 +33345,10 @@
         <v>0</v>
       </c>
       <c r="Y255" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z255" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA255" t="n">
         <v>0</v>
@@ -33385,7 +33385,7 @@
         <v>0</v>
       </c>
       <c r="AK255" s="3" t="n">
-        <v>45962.75</v>
+        <v>45962.71180555555</v>
       </c>
     </row>
     <row r="256">
@@ -33394,27 +33394,27 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -33514,7 +33514,7 @@
         <v>0</v>
       </c>
       <c r="AK256" s="3" t="n">
-        <v>45962.77083333334</v>
+        <v>45962.72916666666</v>
       </c>
     </row>
     <row r="257">
@@ -33523,12 +33523,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -33538,12 +33538,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -33564,13 +33564,13 @@
         </is>
       </c>
       <c r="L257" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M257" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N257" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O257" t="n">
         <v>0</v>
@@ -33603,10 +33603,10 @@
         <v>0</v>
       </c>
       <c r="Y257" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z257" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA257" t="n">
         <v>0</v>
@@ -33643,7 +33643,7 @@
         <v>0</v>
       </c>
       <c r="AK257" s="3" t="n">
-        <v>45962.77083333334</v>
+        <v>45962.75</v>
       </c>
     </row>
     <row r="258">
@@ -33652,12 +33652,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -33667,12 +33667,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -33772,7 +33772,7 @@
         <v>0</v>
       </c>
       <c r="AK258" s="3" t="n">
-        <v>45962.79166666666</v>
+        <v>45962.75</v>
       </c>
     </row>
     <row r="259">
@@ -33781,27 +33781,27 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -33901,7 +33901,7 @@
         <v>0</v>
       </c>
       <c r="AK259" s="3" t="n">
-        <v>45962.79166666666</v>
+        <v>45962.77083333334</v>
       </c>
     </row>
     <row r="260">
@@ -33910,7 +33910,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -33925,12 +33925,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -33951,13 +33951,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M260" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N260" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -33996,10 +33996,10 @@
         <v>0</v>
       </c>
       <c r="AA260" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB260" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC260" t="n">
         <v>0</v>
@@ -34030,7 +34030,7 @@
         <v>0</v>
       </c>
       <c r="AK260" s="3" t="n">
-        <v>45962.85416666666</v>
+        <v>45962.77083333334</v>
       </c>
     </row>
     <row r="261">
@@ -34039,27 +34039,27 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -34159,7 +34159,7 @@
         <v>0</v>
       </c>
       <c r="AK261" s="3" t="n">
-        <v>45962.85416666666</v>
+        <v>45962.79166666666</v>
       </c>
     </row>
     <row r="262">
@@ -34168,12 +34168,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -34183,12 +34183,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -34209,13 +34209,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M262" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N262" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -34248,10 +34248,10 @@
         <v>0</v>
       </c>
       <c r="Y262" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z262" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA262" t="n">
         <v>0</v>
@@ -34288,7 +34288,7 @@
         <v>0</v>
       </c>
       <c r="AK262" s="3" t="n">
-        <v>45962.875</v>
+        <v>45962.79166666666</v>
       </c>
     </row>
     <row r="263">
@@ -34297,7 +34297,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -34312,12 +34312,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -34338,13 +34338,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M263" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N263" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -34383,10 +34383,10 @@
         <v>0</v>
       </c>
       <c r="AA263" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB263" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC263" t="n">
         <v>0</v>
@@ -34417,7 +34417,7 @@
         <v>0</v>
       </c>
       <c r="AK263" s="3" t="n">
-        <v>45962.9375</v>
+        <v>45962.85416666666</v>
       </c>
     </row>
     <row r="264">
@@ -34426,126 +34426,513 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Universidad Católica</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="G264" t="n">
+        <v>0</v>
+      </c>
+      <c r="H264" t="n">
+        <v>0</v>
+      </c>
+      <c r="I264" t="n">
+        <v>0</v>
+      </c>
+      <c r="J264" t="n">
+        <v>0</v>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L264" t="n">
+        <v>0</v>
+      </c>
+      <c r="M264" t="n">
+        <v>0</v>
+      </c>
+      <c r="N264" t="n">
+        <v>0</v>
+      </c>
+      <c r="O264" t="n">
+        <v>0</v>
+      </c>
+      <c r="P264" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q264" t="n">
+        <v>0</v>
+      </c>
+      <c r="R264" t="n">
+        <v>0</v>
+      </c>
+      <c r="S264" t="n">
+        <v>0</v>
+      </c>
+      <c r="T264" t="n">
+        <v>0</v>
+      </c>
+      <c r="U264" t="n">
+        <v>0</v>
+      </c>
+      <c r="V264" t="n">
+        <v>0</v>
+      </c>
+      <c r="W264" t="n">
+        <v>0</v>
+      </c>
+      <c r="X264" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y264" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE264" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF264" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK264" s="3" t="n">
+        <v>45962.85416666666</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="G265" t="n">
+        <v>0</v>
+      </c>
+      <c r="H265" t="n">
+        <v>0</v>
+      </c>
+      <c r="I265" t="n">
+        <v>0</v>
+      </c>
+      <c r="J265" t="n">
+        <v>0</v>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L265" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="M265" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="N265" t="n">
+        <v>15</v>
+      </c>
+      <c r="O265" t="n">
+        <v>0</v>
+      </c>
+      <c r="P265" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q265" t="n">
+        <v>0</v>
+      </c>
+      <c r="R265" t="n">
+        <v>0</v>
+      </c>
+      <c r="S265" t="n">
+        <v>0</v>
+      </c>
+      <c r="T265" t="n">
+        <v>0</v>
+      </c>
+      <c r="U265" t="n">
+        <v>0</v>
+      </c>
+      <c r="V265" t="n">
+        <v>0</v>
+      </c>
+      <c r="W265" t="n">
+        <v>0</v>
+      </c>
+      <c r="X265" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y265" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z265" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE265" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF265" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK265" s="3" t="n">
+        <v>45962.875</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="G266" t="n">
+        <v>0</v>
+      </c>
+      <c r="H266" t="n">
+        <v>0</v>
+      </c>
+      <c r="I266" t="n">
+        <v>0</v>
+      </c>
+      <c r="J266" t="n">
+        <v>0</v>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L266" t="n">
+        <v>0</v>
+      </c>
+      <c r="M266" t="n">
+        <v>0</v>
+      </c>
+      <c r="N266" t="n">
+        <v>0</v>
+      </c>
+      <c r="O266" t="n">
+        <v>0</v>
+      </c>
+      <c r="P266" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q266" t="n">
+        <v>0</v>
+      </c>
+      <c r="R266" t="n">
+        <v>0</v>
+      </c>
+      <c r="S266" t="n">
+        <v>0</v>
+      </c>
+      <c r="T266" t="n">
+        <v>0</v>
+      </c>
+      <c r="U266" t="n">
+        <v>0</v>
+      </c>
+      <c r="V266" t="n">
+        <v>0</v>
+      </c>
+      <c r="W266" t="n">
+        <v>0</v>
+      </c>
+      <c r="X266" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y266" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE266" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF266" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK266" s="3" t="n">
+        <v>45962.9375</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C264" t="inlineStr">
+      <c r="C267" t="inlineStr">
         <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr">
+      <c r="D267" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr">
+      <c r="E267" t="inlineStr">
         <is>
           <t>Portland Timbers</t>
         </is>
       </c>
-      <c r="F264" t="inlineStr">
+      <c r="F267" t="inlineStr">
         <is>
           <t>San Diego</t>
         </is>
       </c>
-      <c r="G264" t="n">
-        <v>0</v>
-      </c>
-      <c r="H264" t="n">
-        <v>0</v>
-      </c>
-      <c r="I264" t="n">
-        <v>0</v>
-      </c>
-      <c r="J264" t="n">
-        <v>0</v>
-      </c>
-      <c r="K264" t="inlineStr">
+      <c r="G267" t="n">
+        <v>0</v>
+      </c>
+      <c r="H267" t="n">
+        <v>0</v>
+      </c>
+      <c r="I267" t="n">
+        <v>0</v>
+      </c>
+      <c r="J267" t="n">
+        <v>0</v>
+      </c>
+      <c r="K267" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L264" t="n">
-        <v>0</v>
-      </c>
-      <c r="M264" t="n">
-        <v>0</v>
-      </c>
-      <c r="N264" t="n">
-        <v>0</v>
-      </c>
-      <c r="O264" t="n">
-        <v>0</v>
-      </c>
-      <c r="P264" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
-      <c r="R264" t="n">
-        <v>0</v>
-      </c>
-      <c r="S264" t="n">
-        <v>0</v>
-      </c>
-      <c r="T264" t="n">
-        <v>0</v>
-      </c>
-      <c r="U264" t="n">
-        <v>0</v>
-      </c>
-      <c r="V264" t="n">
-        <v>0</v>
-      </c>
-      <c r="W264" t="n">
-        <v>0</v>
-      </c>
-      <c r="X264" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y264" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z264" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA264" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB264" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC264" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD264" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE264" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF264" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG264" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH264" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI264" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ264" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK264" s="3" t="n">
+      <c r="L267" t="n">
+        <v>0</v>
+      </c>
+      <c r="M267" t="n">
+        <v>0</v>
+      </c>
+      <c r="N267" t="n">
+        <v>0</v>
+      </c>
+      <c r="O267" t="n">
+        <v>0</v>
+      </c>
+      <c r="P267" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q267" t="n">
+        <v>0</v>
+      </c>
+      <c r="R267" t="n">
+        <v>0</v>
+      </c>
+      <c r="S267" t="n">
+        <v>0</v>
+      </c>
+      <c r="T267" t="n">
+        <v>0</v>
+      </c>
+      <c r="U267" t="n">
+        <v>0</v>
+      </c>
+      <c r="V267" t="n">
+        <v>0</v>
+      </c>
+      <c r="W267" t="n">
+        <v>0</v>
+      </c>
+      <c r="X267" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y267" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE267" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF267" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK267" s="3" t="n">
         <v>45962.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-11-01.xlsx
+++ b/jogos_2025-11-01.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2004,10 +2004,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2133,10 +2133,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Costa Adeje Tenerife W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Costa Adeje Tenerife W</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4326,10 +4326,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Tusker</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tusker</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4842,10 +4842,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6825,22 +6825,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,22 +8244,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9787,27 +9787,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="AK73" s="3" t="n">
-        <v>45962.4375</v>
+        <v>45962.41666666666</v>
       </c>
     </row>
     <row r="74">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10036,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>45962.4375</v>
+        <v>45962.41666666666</v>
       </c>
     </row>
     <row r="75">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11593,27 +11593,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11713,7 +11713,7 @@
         <v>0</v>
       </c>
       <c r="AK87" s="3" t="n">
-        <v>45962.45833333334</v>
+        <v>45962.4375</v>
       </c>
     </row>
     <row r="88">
@@ -11722,27 +11722,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11842,7 +11842,7 @@
         <v>0</v>
       </c>
       <c r="AK88" s="3" t="n">
-        <v>45962.45833333334</v>
+        <v>45962.4375</v>
       </c>
     </row>
     <row r="89">
@@ -11856,22 +11856,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12453,10 +12453,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,22 +12630,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12888,22 +12888,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13098,10 +13098,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,22 +13404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z104" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z106" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15249,10 +15249,10 @@
         <v>2.05</v>
       </c>
       <c r="M115" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N115" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,16 +15285,16 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="Z115" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AA115" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,14 +15375,14 @@
         </is>
       </c>
       <c r="L116" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M116" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N116" t="n">
         <v>3.5</v>
       </c>
-      <c r="M116" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N116" t="n">
-        <v>1.9</v>
-      </c>
       <c r="O116" t="n">
         <v>0</v>
       </c>
@@ -15420,10 +15420,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15549,10 +15549,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="M118" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="N118" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,16 +15672,16 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z118" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA118" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,49 +15762,49 @@
         </is>
       </c>
       <c r="L119" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M119" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N119" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y119" t="n">
         <v>2.05</v>
       </c>
-      <c r="M119" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N119" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O119" t="n">
-        <v>0</v>
-      </c>
-      <c r="P119" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
-      <c r="R119" t="n">
-        <v>0</v>
-      </c>
-      <c r="S119" t="n">
-        <v>0</v>
-      </c>
-      <c r="T119" t="n">
-        <v>0</v>
-      </c>
-      <c r="U119" t="n">
-        <v>0</v>
-      </c>
-      <c r="V119" t="n">
-        <v>0</v>
-      </c>
-      <c r="W119" t="n">
-        <v>0</v>
-      </c>
-      <c r="X119" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y119" t="n">
-        <v>1.85</v>
-      </c>
       <c r="Z119" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z120" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16065,10 +16065,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z124" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z127" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17349,10 +17349,10 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z131" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA131" t="n">
         <v>0</v>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17697,13 +17697,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -17736,10 +17736,10 @@
         <v>0</v>
       </c>
       <c r="Y134" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z134" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA134" t="n">
         <v>0</v>
@@ -17790,7 +17790,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -17955,13 +17955,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>11.44</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -18048,7 +18048,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18058,12 +18058,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18084,13 +18084,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -18123,10 +18123,10 @@
         <v>0</v>
       </c>
       <c r="Y137" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z137" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA137" t="n">
         <v>0</v>
@@ -18177,7 +18177,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18187,12 +18187,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18316,12 +18316,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18342,13 +18342,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -18381,10 +18381,10 @@
         <v>0</v>
       </c>
       <c r="Y139" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z139" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA139" t="n">
         <v>0</v>
@@ -18435,7 +18435,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18445,12 +18445,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18574,12 +18574,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18693,22 +18693,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -18729,13 +18729,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M142" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -18768,10 +18768,10 @@
         <v>0</v>
       </c>
       <c r="Y142" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z142" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA142" t="n">
         <v>0</v>
@@ -18822,7 +18822,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -18832,12 +18832,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -18858,13 +18858,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M143" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -18897,10 +18897,10 @@
         <v>0</v>
       </c>
       <c r="Y143" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z143" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA143" t="n">
         <v>0</v>
@@ -18951,7 +18951,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -18987,13 +18987,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M144" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -19026,10 +19026,10 @@
         <v>0</v>
       </c>
       <c r="Y144" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z144" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA144" t="n">
         <v>0</v>
@@ -19080,7 +19080,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19090,12 +19090,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19219,12 +19219,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19245,13 +19245,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M146" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -19284,10 +19284,10 @@
         <v>0</v>
       </c>
       <c r="Y146" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z146" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA146" t="n">
         <v>0</v>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19374,13 +19374,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M147" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -19413,10 +19413,10 @@
         <v>0</v>
       </c>
       <c r="Y147" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z147" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA147" t="n">
         <v>0</v>
@@ -19467,7 +19467,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19477,12 +19477,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -19606,12 +19606,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -19735,12 +19735,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -19854,7 +19854,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -19864,12 +19864,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -19983,7 +19983,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -19993,12 +19993,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20112,7 +20112,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20122,12 +20122,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20148,13 +20148,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="M153" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="N153" t="n">
-        <v>4.3</v>
+        <v>2.85</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -20187,10 +20187,10 @@
         <v>0</v>
       </c>
       <c r="Y153" t="n">
-        <v>1.75</v>
+        <v>2.18</v>
       </c>
       <c r="Z153" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AA153" t="n">
         <v>0</v>
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20251,12 +20251,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20277,13 +20277,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M154" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -20316,10 +20316,10 @@
         <v>0</v>
       </c>
       <c r="Y154" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z154" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA154" t="n">
         <v>0</v>
@@ -20370,7 +20370,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20380,12 +20380,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20499,7 +20499,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -20509,12 +20509,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -20535,13 +20535,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M156" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N156" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -20574,10 +20574,10 @@
         <v>0</v>
       </c>
       <c r="Y156" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z156" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA156" t="n">
         <v>0</v>
@@ -20628,7 +20628,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -20638,12 +20638,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -20664,13 +20664,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -20703,10 +20703,10 @@
         <v>0</v>
       </c>
       <c r="Y157" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z157" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA157" t="n">
         <v>0</v>
@@ -20757,7 +20757,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -20767,12 +20767,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -20793,13 +20793,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>5</v>
+        <v>1.75</v>
       </c>
       <c r="M158" t="n">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="N158" t="n">
-        <v>1.65</v>
+        <v>4.3</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -20832,10 +20832,10 @@
         <v>0</v>
       </c>
       <c r="Y158" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="Z158" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AA158" t="n">
         <v>0</v>
@@ -20886,22 +20886,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21025,12 +21025,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21051,13 +21051,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>1.82</v>
+        <v>1.23</v>
       </c>
       <c r="M160" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="N160" t="n">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -21090,10 +21090,10 @@
         <v>0</v>
       </c>
       <c r="Y160" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="Z160" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AA160" t="n">
         <v>0</v>
@@ -21154,12 +21154,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21180,13 +21180,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>1.82</v>
+        <v>2.9</v>
       </c>
       <c r="M161" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="N161" t="n">
-        <v>4.5</v>
+        <v>2.25</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -21219,10 +21219,10 @@
         <v>0</v>
       </c>
       <c r="Y161" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="Z161" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AA161" t="n">
         <v>0</v>
@@ -21402,7 +21402,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21412,12 +21412,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21531,7 +21531,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -21541,12 +21541,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -21567,13 +21567,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M164" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -21606,10 +21606,10 @@
         <v>0</v>
       </c>
       <c r="Y164" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z164" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA164" t="n">
         <v>0</v>
@@ -21660,7 +21660,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -21670,12 +21670,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -21799,12 +21799,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -21918,7 +21918,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -21928,12 +21928,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -21954,13 +21954,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M167" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -21999,10 +21999,10 @@
         <v>0</v>
       </c>
       <c r="AA167" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB167" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC167" t="n">
         <v>0</v>
@@ -22176,7 +22176,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22186,12 +22186,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22212,13 +22212,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N169" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -22251,10 +22251,10 @@
         <v>0</v>
       </c>
       <c r="Y169" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z169" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA169" t="n">
         <v>0</v>
@@ -22305,7 +22305,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -22315,12 +22315,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22341,13 +22341,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M170" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N170" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -22386,10 +22386,10 @@
         <v>0</v>
       </c>
       <c r="AA170" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB170" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC170" t="n">
         <v>0</v>
@@ -22692,7 +22692,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -22728,13 +22728,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N173" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -22767,10 +22767,10 @@
         <v>0</v>
       </c>
       <c r="Y173" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z173" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA173" t="n">
         <v>0</v>
@@ -22821,7 +22821,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -22831,12 +22831,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -22950,7 +22950,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -22960,12 +22960,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23089,12 +23089,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23218,12 +23218,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23337,7 +23337,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -23347,12 +23347,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23373,13 +23373,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M178" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N178" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -23412,10 +23412,10 @@
         <v>0</v>
       </c>
       <c r="Y178" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z178" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA178" t="n">
         <v>0</v>
@@ -23466,7 +23466,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -23476,12 +23476,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -23502,13 +23502,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M179" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N179" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -23541,10 +23541,10 @@
         <v>0</v>
       </c>
       <c r="Y179" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z179" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA179" t="n">
         <v>0</v>
@@ -23595,7 +23595,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -23605,12 +23605,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -23631,13 +23631,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M180" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N180" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -23670,10 +23670,10 @@
         <v>0</v>
       </c>
       <c r="Y180" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z180" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA180" t="n">
         <v>0</v>
@@ -23724,7 +23724,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -23734,12 +23734,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -23853,7 +23853,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -23863,12 +23863,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -23889,13 +23889,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M182" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N182" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -23928,10 +23928,10 @@
         <v>0</v>
       </c>
       <c r="Y182" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z182" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA182" t="n">
         <v>0</v>
@@ -23982,7 +23982,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -23992,12 +23992,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24111,7 +24111,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -24121,12 +24121,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24240,7 +24240,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -24250,12 +24250,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24276,13 +24276,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M185" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -24315,10 +24315,10 @@
         <v>0</v>
       </c>
       <c r="Y185" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z185" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA185" t="n">
         <v>0</v>
@@ -24369,7 +24369,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -24379,12 +24379,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24405,13 +24405,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M186" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N186" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -24444,10 +24444,10 @@
         <v>0</v>
       </c>
       <c r="Y186" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z186" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA186" t="n">
         <v>0</v>
@@ -24498,7 +24498,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -24508,12 +24508,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -24534,13 +24534,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M187" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N187" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -24573,10 +24573,10 @@
         <v>0</v>
       </c>
       <c r="Y187" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z187" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA187" t="n">
         <v>0</v>
@@ -24627,7 +24627,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -24637,12 +24637,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -24756,7 +24756,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -24766,12 +24766,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -25014,22 +25014,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25143,7 +25143,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -25153,12 +25153,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25282,12 +25282,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25401,22 +25401,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -25530,7 +25530,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -25540,12 +25540,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -25566,13 +25566,13 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M195" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N195" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -25605,16 +25605,16 @@
         <v>0</v>
       </c>
       <c r="Y195" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z195" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AA195" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB195" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC195" t="n">
         <v>0</v>
@@ -25659,22 +25659,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -25788,22 +25788,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -25927,12 +25927,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -25953,13 +25953,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M198" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N198" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -25992,16 +25992,16 @@
         <v>0</v>
       </c>
       <c r="Y198" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z198" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA198" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB198" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC198" t="n">
         <v>0</v>
@@ -26056,12 +26056,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26175,7 +26175,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26185,12 +26185,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26433,7 +26433,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -26443,12 +26443,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -26562,7 +26562,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -26572,12 +26572,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -26691,7 +26691,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -26701,12 +26701,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -26820,7 +26820,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -26830,12 +26830,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -26949,7 +26949,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -26959,12 +26959,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27078,22 +27078,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27207,7 +27207,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -27217,12 +27217,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27336,22 +27336,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27465,7 +27465,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -27475,12 +27475,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -27604,12 +27604,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27723,7 +27723,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -27733,12 +27733,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -27852,7 +27852,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -27862,12 +27862,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -27981,7 +27981,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -27991,12 +27991,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28110,7 +28110,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -28120,12 +28120,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28368,7 +28368,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -28378,12 +28378,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -28404,13 +28404,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M217" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N217" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -28443,10 +28443,10 @@
         <v>0</v>
       </c>
       <c r="Y217" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z217" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA217" t="n">
         <v>0</v>
@@ -28497,7 +28497,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -28507,12 +28507,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -28533,13 +28533,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="N218" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -28572,16 +28572,16 @@
         <v>0</v>
       </c>
       <c r="Y218" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z218" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA218" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB218" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC218" t="n">
         <v>0</v>
@@ -28626,7 +28626,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -28636,12 +28636,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -28662,13 +28662,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M219" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N219" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -28701,10 +28701,10 @@
         <v>0</v>
       </c>
       <c r="Y219" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z219" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA219" t="n">
         <v>0</v>
@@ -28755,7 +28755,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -28765,12 +28765,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -28884,7 +28884,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -28894,12 +28894,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -28920,13 +28920,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M221" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="N221" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -28959,16 +28959,16 @@
         <v>0</v>
       </c>
       <c r="Y221" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z221" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA221" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB221" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC221" t="n">
         <v>0</v>
@@ -29013,7 +29013,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29023,12 +29023,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29142,7 +29142,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29178,13 +29178,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M223" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N223" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -29217,10 +29217,10 @@
         <v>0</v>
       </c>
       <c r="Y223" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Z223" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA223" t="n">
         <v>0</v>
@@ -29271,7 +29271,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29281,12 +29281,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29307,13 +29307,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M224" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N224" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -29346,10 +29346,10 @@
         <v>0</v>
       </c>
       <c r="Y224" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Z224" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA224" t="n">
         <v>0</v>
@@ -29400,7 +29400,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -29410,12 +29410,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -29436,13 +29436,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M225" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N225" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -29475,10 +29475,10 @@
         <v>0</v>
       </c>
       <c r="Y225" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z225" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA225" t="n">
         <v>0</v>
@@ -29539,12 +29539,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -29565,13 +29565,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>1.14</v>
+        <v>2.55</v>
       </c>
       <c r="M226" t="n">
-        <v>8</v>
+        <v>3.75</v>
       </c>
       <c r="N226" t="n">
-        <v>19</v>
+        <v>2.55</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -29604,16 +29604,16 @@
         <v>0</v>
       </c>
       <c r="Y226" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z226" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA226" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB226" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC226" t="n">
         <v>0</v>
@@ -29658,7 +29658,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -29668,12 +29668,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -29694,13 +29694,13 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M227" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N227" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -29739,10 +29739,10 @@
         <v>0</v>
       </c>
       <c r="AA227" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB227" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC227" t="n">
         <v>0</v>
@@ -29787,7 +29787,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -29797,12 +29797,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -29916,7 +29916,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -29926,12 +29926,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -29952,13 +29952,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N229" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -29991,10 +29991,10 @@
         <v>0</v>
       </c>
       <c r="Y229" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z229" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA229" t="n">
         <v>0</v>
@@ -30045,7 +30045,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -30055,12 +30055,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30081,13 +30081,13 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M230" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N230" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -30120,10 +30120,10 @@
         <v>0</v>
       </c>
       <c r="Y230" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z230" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA230" t="n">
         <v>0</v>
@@ -30174,7 +30174,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -30184,12 +30184,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -30432,7 +30432,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -30442,12 +30442,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -30561,7 +30561,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -30571,12 +30571,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -30690,7 +30690,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -30700,12 +30700,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -30726,13 +30726,13 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="M235" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N235" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O235" t="n">
         <v>0</v>
@@ -30765,10 +30765,10 @@
         <v>0</v>
       </c>
       <c r="Y235" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z235" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA235" t="n">
         <v>0</v>
@@ -30819,7 +30819,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -30829,12 +30829,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -30855,13 +30855,13 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M236" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N236" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O236" t="n">
         <v>0</v>
@@ -30894,10 +30894,10 @@
         <v>0</v>
       </c>
       <c r="Y236" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z236" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA236" t="n">
         <v>0</v>
@@ -30948,22 +30948,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31077,7 +31077,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -31087,12 +31087,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31206,22 +31206,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M239" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N239" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -31281,10 +31281,10 @@
         <v>0</v>
       </c>
       <c r="Y239" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z239" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA239" t="n">
         <v>0</v>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -31345,12 +31345,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -31464,7 +31464,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -31474,12 +31474,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -31593,22 +31593,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -31851,7 +31851,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -31861,12 +31861,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -31980,22 +31980,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32109,7 +32109,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -32119,12 +32119,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -32145,13 +32145,13 @@
         </is>
       </c>
       <c r="L246" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M246" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N246" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O246" t="n">
         <v>0</v>
@@ -32184,10 +32184,10 @@
         <v>0</v>
       </c>
       <c r="Y246" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z246" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA246" t="n">
         <v>0</v>
@@ -32403,13 +32403,13 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M248" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N248" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O248" t="n">
         <v>0</v>
@@ -32442,10 +32442,10 @@
         <v>0</v>
       </c>
       <c r="Y248" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z248" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA248" t="n">
         <v>0</v>
@@ -32790,13 +32790,13 @@
         </is>
       </c>
       <c r="L251" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M251" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N251" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O251" t="n">
         <v>0</v>
@@ -32835,10 +32835,10 @@
         <v>0</v>
       </c>
       <c r="AA251" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB251" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC251" t="n">
         <v>0</v>
@@ -32883,7 +32883,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -32893,12 +32893,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -32919,13 +32919,13 @@
         </is>
       </c>
       <c r="L252" t="n">
-        <v>2.4</v>
+        <v>1.55</v>
       </c>
       <c r="M252" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="N252" t="n">
-        <v>2.7</v>
+        <v>5.3</v>
       </c>
       <c r="O252" t="n">
         <v>0</v>
@@ -32958,16 +32958,16 @@
         <v>0</v>
       </c>
       <c r="Y252" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z252" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA252" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AB252" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC252" t="n">
         <v>0</v>
@@ -33012,7 +33012,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -33022,12 +33022,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -33048,13 +33048,13 @@
         </is>
       </c>
       <c r="L253" t="n">
-        <v>1.55</v>
+        <v>2.4</v>
       </c>
       <c r="M253" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="N253" t="n">
-        <v>5.3</v>
+        <v>2.7</v>
       </c>
       <c r="O253" t="n">
         <v>0</v>
@@ -33087,16 +33087,16 @@
         <v>0</v>
       </c>
       <c r="Y253" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z253" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA253" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AB253" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC253" t="n">
         <v>0</v>
@@ -33528,7 +33528,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -33538,12 +33538,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -33564,13 +33564,13 @@
         </is>
       </c>
       <c r="L257" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M257" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N257" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O257" t="n">
         <v>0</v>
@@ -33603,10 +33603,10 @@
         <v>0</v>
       </c>
       <c r="Y257" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z257" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA257" t="n">
         <v>0</v>
@@ -33657,7 +33657,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -33667,12 +33667,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -33693,13 +33693,13 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M258" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N258" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O258" t="n">
         <v>0</v>
@@ -33732,10 +33732,10 @@
         <v>0</v>
       </c>
       <c r="Y258" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z258" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA258" t="n">
         <v>0</v>
@@ -34302,7 +34302,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -34312,12 +34312,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -34338,13 +34338,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N263" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -34383,10 +34383,10 @@
         <v>0</v>
       </c>
       <c r="AA263" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB263" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC263" t="n">
         <v>0</v>
@@ -34431,7 +34431,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -34441,12 +34441,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -34467,13 +34467,13 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M264" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N264" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O264" t="n">
         <v>0</v>
@@ -34512,10 +34512,10 @@
         <v>0</v>
       </c>
       <c r="AA264" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB264" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC264" t="n">
         <v>0</v>

--- a/jogos_2025-11-01.xlsx
+++ b/jogos_2025-11-01.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.3</v>
+        <v>4.6</v>
       </c>
       <c r="M12" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="N12" t="n">
-        <v>8.5</v>
+        <v>1.63</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2004,10 +2004,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="M13" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="N13" t="n">
-        <v>1.63</v>
+        <v>8.5</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2133,10 +2133,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Costa Adeje Tenerife W</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Costa Adeje Tenerife W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4842,10 +4842,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5316,10 +5316,10 @@
         <v>1.95</v>
       </c>
       <c r="M38" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="N38" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,16 +5352,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="M41" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N41" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,7 +5739,7 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="Z41" t="n">
         <v>2.1</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,49 +6990,49 @@
         </is>
       </c>
       <c r="L51" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M51" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N51" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z51" t="n">
         <v>2.1</v>
-      </c>
-      <c r="M51" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N51" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>1.88</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.37</v>
+        <v>1.8</v>
       </c>
       <c r="M52" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="N52" t="n">
-        <v>8.5</v>
+        <v>4.2</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,22 +8373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,22 +8889,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9018,22 +9018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,22 +9792,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10506,10 +10506,10 @@
         <v>0</v>
       </c>
       <c r="W78" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X78" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y78" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10764,10 +10764,10 @@
         <v>0</v>
       </c>
       <c r="W80" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="X80" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y80" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11937,10 +11937,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11985,22 +11985,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,22 +12114,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,22 +12243,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,22 +12372,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,22 +12501,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,22 +12630,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,22 +12759,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12888,22 +12888,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13098,10 +13098,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -13146,22 +13146,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13404,22 +13404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,22 +13662,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z105" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z106" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z110" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="M115" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N115" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,16 +15285,16 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA115" t="n">
         <v>1.95</v>
       </c>
-      <c r="AA115" t="n">
-        <v>0</v>
-      </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.95</v>
+        <v>3.5</v>
       </c>
       <c r="M116" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="N116" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15420,10 +15420,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="M117" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="N117" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,16 +15543,16 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z117" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA117" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,16 +15672,16 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z118" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,14 +15762,14 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="M119" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N119" t="n">
         <v>3.3</v>
       </c>
-      <c r="N119" t="n">
-        <v>2.6</v>
-      </c>
       <c r="O119" t="n">
         <v>0</v>
       </c>
@@ -15801,16 +15801,16 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="Z119" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="AA119" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,55 +16020,55 @@
         </is>
       </c>
       <c r="L121" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M121" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N121" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z121" t="n">
         <v>1.95</v>
       </c>
-      <c r="M121" t="n">
-        <v>4</v>
-      </c>
-      <c r="N121" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O121" t="n">
-        <v>0</v>
-      </c>
-      <c r="P121" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
-      <c r="R121" t="n">
-        <v>0</v>
-      </c>
-      <c r="S121" t="n">
-        <v>0</v>
-      </c>
-      <c r="T121" t="n">
-        <v>0</v>
-      </c>
-      <c r="U121" t="n">
-        <v>0</v>
-      </c>
-      <c r="V121" t="n">
-        <v>0</v>
-      </c>
-      <c r="W121" t="n">
-        <v>0</v>
-      </c>
-      <c r="X121" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y121" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z121" t="n">
-        <v>0</v>
-      </c>
       <c r="AA121" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,10 +16317,10 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z123" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.9</v>
+        <v>1.62</v>
       </c>
       <c r="M124" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="N124" t="n">
-        <v>2.3</v>
+        <v>5.2</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Z124" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z127" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.35</v>
+        <v>2.9</v>
       </c>
       <c r="M131" t="n">
-        <v>3.38</v>
+        <v>3.65</v>
       </c>
       <c r="N131" t="n">
-        <v>2.83</v>
+        <v>2.3</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17349,10 +17349,10 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="Z131" t="n">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="AA131" t="n">
         <v>0</v>
@@ -17532,7 +17532,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17568,13 +17568,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -17607,10 +17607,10 @@
         <v>0</v>
       </c>
       <c r="Y133" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z133" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA133" t="n">
         <v>0</v>
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17697,13 +17697,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -17736,10 +17736,10 @@
         <v>0</v>
       </c>
       <c r="Y134" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z134" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA134" t="n">
         <v>0</v>
@@ -17800,7 +17800,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -17955,13 +17955,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>11.44</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -18048,7 +18048,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18058,12 +18058,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18084,13 +18084,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -18123,10 +18123,10 @@
         <v>0</v>
       </c>
       <c r="Y137" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z137" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA137" t="n">
         <v>0</v>
@@ -18187,7 +18187,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18316,12 +18316,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18342,13 +18342,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -18381,10 +18381,10 @@
         <v>0</v>
       </c>
       <c r="Y139" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z139" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA139" t="n">
         <v>0</v>
@@ -18435,7 +18435,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18445,12 +18445,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18471,13 +18471,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -18510,10 +18510,10 @@
         <v>0</v>
       </c>
       <c r="Y140" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z140" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA140" t="n">
         <v>0</v>
@@ -18564,7 +18564,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18574,12 +18574,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18600,13 +18600,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M141" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -18639,10 +18639,10 @@
         <v>0</v>
       </c>
       <c r="Y141" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z141" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA141" t="n">
         <v>0</v>
@@ -18693,7 +18693,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -18703,12 +18703,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -18729,13 +18729,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>5</v>
+        <v>1.82</v>
       </c>
       <c r="M142" t="n">
-        <v>4.05</v>
+        <v>3.55</v>
       </c>
       <c r="N142" t="n">
-        <v>1.65</v>
+        <v>4.5</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -18768,10 +18768,10 @@
         <v>0</v>
       </c>
       <c r="Y142" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="Z142" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AA142" t="n">
         <v>0</v>
@@ -18822,7 +18822,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -18832,12 +18832,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -18858,13 +18858,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -18897,10 +18897,10 @@
         <v>0</v>
       </c>
       <c r="Y143" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z143" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA143" t="n">
         <v>0</v>
@@ -18951,7 +18951,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -18987,13 +18987,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="M144" t="n">
-        <v>3.8</v>
+        <v>6.5</v>
       </c>
       <c r="N144" t="n">
-        <v>4.5</v>
+        <v>11.44</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -19026,10 +19026,10 @@
         <v>0</v>
       </c>
       <c r="Y144" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z144" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA144" t="n">
         <v>0</v>
@@ -19080,7 +19080,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19090,12 +19090,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19116,13 +19116,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M145" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -19155,10 +19155,10 @@
         <v>0</v>
       </c>
       <c r="Y145" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z145" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA145" t="n">
         <v>0</v>
@@ -19209,7 +19209,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19219,12 +19219,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19245,13 +19245,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="M146" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N146" t="n">
-        <v>3.05</v>
+        <v>7.5</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -19284,10 +19284,10 @@
         <v>0</v>
       </c>
       <c r="Y146" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="Z146" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AA146" t="n">
         <v>0</v>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19374,13 +19374,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>3.6</v>
+        <v>2.35</v>
       </c>
       <c r="M147" t="n">
-        <v>3.85</v>
+        <v>3.38</v>
       </c>
       <c r="N147" t="n">
-        <v>1.95</v>
+        <v>2.83</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -19413,10 +19413,10 @@
         <v>0</v>
       </c>
       <c r="Y147" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="Z147" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AA147" t="n">
         <v>0</v>
@@ -19467,7 +19467,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19477,12 +19477,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19503,13 +19503,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M148" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N148" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -19542,10 +19542,10 @@
         <v>0</v>
       </c>
       <c r="Y148" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z148" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA148" t="n">
         <v>0</v>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -19606,12 +19606,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -19632,13 +19632,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -19671,10 +19671,10 @@
         <v>0</v>
       </c>
       <c r="Y149" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z149" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA149" t="n">
         <v>0</v>
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -19735,12 +19735,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -19854,7 +19854,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -19864,12 +19864,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -19890,13 +19890,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M151" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -19929,10 +19929,10 @@
         <v>0</v>
       </c>
       <c r="Y151" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z151" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA151" t="n">
         <v>0</v>
@@ -19983,7 +19983,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -19993,12 +19993,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20251,12 +20251,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20277,13 +20277,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="M154" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="N154" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -20316,10 +20316,10 @@
         <v>0</v>
       </c>
       <c r="Y154" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="Z154" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AA154" t="n">
         <v>0</v>
@@ -20370,7 +20370,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20380,12 +20380,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20499,7 +20499,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -20509,12 +20509,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -20535,13 +20535,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M156" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -20574,10 +20574,10 @@
         <v>0</v>
       </c>
       <c r="Y156" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z156" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA156" t="n">
         <v>0</v>
@@ -20628,7 +20628,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -20638,12 +20638,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -20757,7 +20757,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -20767,12 +20767,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -20793,13 +20793,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -20832,10 +20832,10 @@
         <v>0</v>
       </c>
       <c r="Y158" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z158" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA158" t="n">
         <v>0</v>
@@ -20886,22 +20886,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21015,22 +21015,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21051,13 +21051,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M160" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N160" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -21090,10 +21090,10 @@
         <v>0</v>
       </c>
       <c r="Y160" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z160" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA160" t="n">
         <v>0</v>
@@ -21154,12 +21154,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21180,13 +21180,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>2.9</v>
+        <v>1.82</v>
       </c>
       <c r="M161" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="N161" t="n">
-        <v>2.25</v>
+        <v>4.3</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -21219,10 +21219,10 @@
         <v>0</v>
       </c>
       <c r="Y161" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="Z161" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AA161" t="n">
         <v>0</v>
@@ -21402,7 +21402,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21412,12 +21412,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21438,13 +21438,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M163" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N163" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -21477,10 +21477,10 @@
         <v>0</v>
       </c>
       <c r="Y163" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z163" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA163" t="n">
         <v>0</v>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -21541,12 +21541,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -21567,13 +21567,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>2.7</v>
+        <v>1.33</v>
       </c>
       <c r="M164" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="N164" t="n">
-        <v>2.7</v>
+        <v>8.5</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -21606,16 +21606,16 @@
         <v>0</v>
       </c>
       <c r="Y164" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z164" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA164" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB164" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC164" t="n">
         <v>0</v>
@@ -21660,7 +21660,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -21670,12 +21670,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -21799,12 +21799,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -21918,7 +21918,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -21928,12 +21928,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -21954,13 +21954,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>1.33</v>
+        <v>2.55</v>
       </c>
       <c r="M167" t="n">
-        <v>5.5</v>
+        <v>2.65</v>
       </c>
       <c r="N167" t="n">
-        <v>8.5</v>
+        <v>3.2</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -21987,10 +21987,10 @@
         <v>0</v>
       </c>
       <c r="W167" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="X167" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y167" t="n">
         <v>0</v>
@@ -21999,10 +21999,10 @@
         <v>0</v>
       </c>
       <c r="AA167" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB167" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC167" t="n">
         <v>0</v>
@@ -22047,7 +22047,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -22057,12 +22057,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22083,13 +22083,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M168" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N168" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="Y168" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z168" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA168" t="n">
         <v>0</v>
@@ -22176,7 +22176,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22186,12 +22186,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22305,7 +22305,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -22315,12 +22315,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22434,7 +22434,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22444,12 +22444,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -22470,13 +22470,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M171" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N171" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -22509,10 +22509,10 @@
         <v>0</v>
       </c>
       <c r="Y171" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z171" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA171" t="n">
         <v>0</v>
@@ -22692,7 +22692,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -22821,7 +22821,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -22831,12 +22831,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -22950,7 +22950,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -22960,12 +22960,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -22986,13 +22986,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="M175" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="N175" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -23089,12 +23089,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23208,7 +23208,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23218,12 +23218,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23244,13 +23244,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M177" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -23283,10 +23283,10 @@
         <v>0</v>
       </c>
       <c r="Y177" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z177" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA177" t="n">
         <v>0</v>
@@ -23337,7 +23337,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -23347,12 +23347,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23373,13 +23373,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M178" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N178" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -23412,10 +23412,10 @@
         <v>0</v>
       </c>
       <c r="Y178" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z178" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA178" t="n">
         <v>0</v>
@@ -23466,7 +23466,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -23476,12 +23476,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -23502,13 +23502,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M179" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N179" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -23541,10 +23541,10 @@
         <v>0</v>
       </c>
       <c r="Y179" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z179" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA179" t="n">
         <v>0</v>
@@ -23595,7 +23595,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -23605,12 +23605,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -23734,12 +23734,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -23853,7 +23853,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -23863,12 +23863,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -23889,13 +23889,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M182" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N182" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -23928,10 +23928,10 @@
         <v>0</v>
       </c>
       <c r="Y182" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z182" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA182" t="n">
         <v>0</v>
@@ -23982,7 +23982,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -23992,12 +23992,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24018,13 +24018,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M183" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N183" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -24057,10 +24057,10 @@
         <v>0</v>
       </c>
       <c r="Y183" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z183" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA183" t="n">
         <v>0</v>
@@ -24111,7 +24111,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -24121,12 +24121,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24240,7 +24240,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -24250,12 +24250,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24276,13 +24276,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N185" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -24315,10 +24315,10 @@
         <v>0</v>
       </c>
       <c r="Y185" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z185" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA185" t="n">
         <v>0</v>
@@ -24369,7 +24369,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -24379,12 +24379,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24405,13 +24405,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M186" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N186" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -24444,10 +24444,10 @@
         <v>0</v>
       </c>
       <c r="Y186" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z186" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA186" t="n">
         <v>0</v>
@@ -24498,7 +24498,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -24508,12 +24508,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -24534,13 +24534,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M187" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N187" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -24573,10 +24573,10 @@
         <v>0</v>
       </c>
       <c r="Y187" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z187" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA187" t="n">
         <v>0</v>
@@ -24627,7 +24627,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -24637,12 +24637,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -24766,12 +24766,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -24880,12 +24880,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -24895,12 +24895,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25000,7 +25000,7 @@
         <v>0</v>
       </c>
       <c r="AK190" s="3" t="n">
-        <v>45962.55208333334</v>
+        <v>45962.54166666666</v>
       </c>
     </row>
     <row r="191">
@@ -25009,12 +25009,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -25024,12 +25024,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25129,7 +25129,7 @@
         <v>0</v>
       </c>
       <c r="AK191" s="3" t="n">
-        <v>45962.5625</v>
+        <v>45962.55208333334</v>
       </c>
     </row>
     <row r="192">
@@ -25143,7 +25143,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -25153,12 +25153,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25282,12 +25282,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25401,22 +25401,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -25530,22 +25530,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -25659,22 +25659,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -25788,7 +25788,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -25798,12 +25798,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -25824,13 +25824,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M197" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N197" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -25863,16 +25863,16 @@
         <v>0</v>
       </c>
       <c r="Y197" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z197" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA197" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB197" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC197" t="n">
         <v>0</v>
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -25927,12 +25927,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -25953,13 +25953,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N198" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -25992,16 +25992,16 @@
         <v>0</v>
       </c>
       <c r="Y198" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z198" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AA198" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB198" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC198" t="n">
         <v>0</v>
@@ -26056,12 +26056,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26175,22 +26175,22 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26299,12 +26299,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26314,12 +26314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26419,7 +26419,7 @@
         <v>0</v>
       </c>
       <c r="AK201" s="3" t="n">
-        <v>45962.58333333334</v>
+        <v>45962.5625</v>
       </c>
     </row>
     <row r="202">
@@ -26433,7 +26433,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -26443,12 +26443,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -26562,7 +26562,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -26572,12 +26572,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -26691,7 +26691,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -26701,12 +26701,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -26820,7 +26820,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -26830,12 +26830,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -26949,7 +26949,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -26959,12 +26959,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27078,7 +27078,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -27088,12 +27088,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27217,12 +27217,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27336,22 +27336,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27594,22 +27594,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27723,7 +27723,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -27733,12 +27733,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -27852,7 +27852,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -27862,12 +27862,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -27981,7 +27981,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -27991,12 +27991,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28110,7 +28110,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -28120,12 +28120,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28234,12 +28234,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28249,12 +28249,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28275,13 +28275,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M216" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="N216" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -28320,10 +28320,10 @@
         <v>0</v>
       </c>
       <c r="AA216" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB216" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC216" t="n">
         <v>0</v>
@@ -28354,7 +28354,7 @@
         <v>0</v>
       </c>
       <c r="AK216" s="3" t="n">
-        <v>45962.59375</v>
+        <v>45962.58333333334</v>
       </c>
     </row>
     <row r="217">
@@ -28363,12 +28363,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -28378,12 +28378,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -28404,13 +28404,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M217" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="N217" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -28449,10 +28449,10 @@
         <v>0</v>
       </c>
       <c r="AA217" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB217" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC217" t="n">
         <v>0</v>
@@ -28483,7 +28483,7 @@
         <v>0</v>
       </c>
       <c r="AK217" s="3" t="n">
-        <v>45962.60416666666</v>
+        <v>45962.59375</v>
       </c>
     </row>
     <row r="218">
@@ -28497,7 +28497,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -28507,12 +28507,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -28626,7 +28626,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -28636,12 +28636,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -28662,13 +28662,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>2.7</v>
+        <v>2.04</v>
       </c>
       <c r="M219" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="N219" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -28701,10 +28701,10 @@
         <v>0</v>
       </c>
       <c r="Y219" t="n">
-        <v>1.65</v>
+        <v>2.13</v>
       </c>
       <c r="Z219" t="n">
-        <v>2.2</v>
+        <v>1.61</v>
       </c>
       <c r="AA219" t="n">
         <v>0</v>
@@ -28755,7 +28755,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -28765,12 +28765,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -28884,7 +28884,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -28894,12 +28894,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -28920,13 +28920,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M221" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="N221" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -28959,16 +28959,16 @@
         <v>0</v>
       </c>
       <c r="Y221" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z221" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA221" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB221" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC221" t="n">
         <v>0</v>
@@ -29013,7 +29013,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29023,12 +29023,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29049,13 +29049,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M222" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N222" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -29088,10 +29088,10 @@
         <v>0</v>
       </c>
       <c r="Y222" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z222" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA222" t="n">
         <v>0</v>
@@ -29142,7 +29142,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29271,7 +29271,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29281,12 +29281,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29307,13 +29307,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M224" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N224" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -29346,10 +29346,10 @@
         <v>0</v>
       </c>
       <c r="Y224" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Z224" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA224" t="n">
         <v>0</v>
@@ -29395,12 +29395,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -29410,12 +29410,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -29436,13 +29436,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="M225" t="n">
-        <v>8</v>
+        <v>6.3</v>
       </c>
       <c r="N225" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -29475,16 +29475,16 @@
         <v>0</v>
       </c>
       <c r="Y225" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="Z225" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AA225" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB225" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC225" t="n">
         <v>0</v>
@@ -29515,7 +29515,7 @@
         <v>0</v>
       </c>
       <c r="AK225" s="3" t="n">
-        <v>45962.61458333334</v>
+        <v>45962.60416666666</v>
       </c>
     </row>
     <row r="226">
@@ -29787,7 +29787,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -29797,12 +29797,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -29916,7 +29916,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -29926,12 +29926,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -29952,13 +29952,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M229" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="N229" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -29985,10 +29985,10 @@
         <v>0</v>
       </c>
       <c r="W229" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X229" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y229" t="n">
         <v>0</v>
@@ -30045,7 +30045,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -30055,12 +30055,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30081,13 +30081,13 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M230" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N230" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -30120,10 +30120,10 @@
         <v>0</v>
       </c>
       <c r="Y230" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z230" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA230" t="n">
         <v>0</v>
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -30432,7 +30432,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -30442,12 +30442,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -30468,13 +30468,13 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M233" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N233" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O233" t="n">
         <v>0</v>
@@ -30507,10 +30507,10 @@
         <v>0</v>
       </c>
       <c r="Y233" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z233" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA233" t="n">
         <v>0</v>
@@ -30561,7 +30561,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -30571,12 +30571,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -30690,7 +30690,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -30700,12 +30700,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -30726,13 +30726,13 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M235" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N235" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O235" t="n">
         <v>0</v>
@@ -30765,10 +30765,10 @@
         <v>0</v>
       </c>
       <c r="Y235" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z235" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA235" t="n">
         <v>0</v>
@@ -30819,7 +30819,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -30829,12 +30829,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -30855,13 +30855,13 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="M236" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N236" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O236" t="n">
         <v>0</v>
@@ -30894,10 +30894,10 @@
         <v>0</v>
       </c>
       <c r="Y236" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z236" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA236" t="n">
         <v>0</v>
@@ -31077,22 +31077,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31113,13 +31113,13 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M238" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N238" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -31152,10 +31152,10 @@
         <v>0</v>
       </c>
       <c r="Y238" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z238" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA238" t="n">
         <v>0</v>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -31345,12 +31345,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -31371,13 +31371,13 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M240" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N240" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -31410,10 +31410,10 @@
         <v>0</v>
       </c>
       <c r="Y240" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z240" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA240" t="n">
         <v>0</v>
@@ -31593,22 +31593,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -31732,12 +31732,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -32109,7 +32109,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -32119,12 +32119,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -32145,13 +32145,13 @@
         </is>
       </c>
       <c r="L246" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M246" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N246" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O246" t="n">
         <v>0</v>
@@ -32184,10 +32184,10 @@
         <v>0</v>
       </c>
       <c r="Y246" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z246" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA246" t="n">
         <v>0</v>
@@ -32625,7 +32625,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -32635,12 +32635,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -32661,13 +32661,13 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M250" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N250" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O250" t="n">
         <v>0</v>
@@ -32706,10 +32706,10 @@
         <v>0</v>
       </c>
       <c r="AA250" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB250" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC250" t="n">
         <v>0</v>
@@ -32754,7 +32754,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -32764,12 +32764,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -32790,13 +32790,13 @@
         </is>
       </c>
       <c r="L251" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M251" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N251" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O251" t="n">
         <v>0</v>
@@ -32835,10 +32835,10 @@
         <v>0</v>
       </c>
       <c r="AA251" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB251" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC251" t="n">
         <v>0</v>
@@ -32883,7 +32883,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -32893,12 +32893,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>CE Europa</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -32919,13 +32919,13 @@
         </is>
       </c>
       <c r="L252" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M252" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N252" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O252" t="n">
         <v>0</v>
@@ -32958,16 +32958,16 @@
         <v>0</v>
       </c>
       <c r="Y252" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z252" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA252" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB252" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC252" t="n">
         <v>0</v>
@@ -33012,7 +33012,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -33022,12 +33022,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -33048,13 +33048,13 @@
         </is>
       </c>
       <c r="L253" t="n">
-        <v>2.4</v>
+        <v>1.55</v>
       </c>
       <c r="M253" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="N253" t="n">
-        <v>2.7</v>
+        <v>5.3</v>
       </c>
       <c r="O253" t="n">
         <v>0</v>
@@ -33087,16 +33087,16 @@
         <v>0</v>
       </c>
       <c r="Y253" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z253" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA253" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AB253" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC253" t="n">
         <v>0</v>
@@ -33141,7 +33141,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -33151,12 +33151,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>CE Europa</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -33177,13 +33177,13 @@
         </is>
       </c>
       <c r="L254" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M254" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N254" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O254" t="n">
         <v>0</v>
@@ -33222,10 +33222,10 @@
         <v>0</v>
       </c>
       <c r="AA254" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB254" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC254" t="n">
         <v>0</v>
@@ -33786,7 +33786,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -33796,12 +33796,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -33915,7 +33915,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -33925,12 +33925,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -34302,7 +34302,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -34312,12 +34312,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -34338,13 +34338,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M263" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N263" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -34383,10 +34383,10 @@
         <v>0</v>
       </c>
       <c r="AA263" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB263" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC263" t="n">
         <v>0</v>
@@ -34431,7 +34431,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -34441,12 +34441,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -34467,13 +34467,13 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M264" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N264" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O264" t="n">
         <v>0</v>
@@ -34512,10 +34512,10 @@
         <v>0</v>
       </c>
       <c r="AA264" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB264" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC264" t="n">
         <v>0</v>
